--- a/v4/03_extracted/SituationChap_VALIDATION_2025.xlsx
+++ b/v4/03_extracted/SituationChap_VALIDATION_2025.xlsx
@@ -1497,34 +1497,34 @@
         <v>139860</v>
       </c>
       <c r="M13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="O13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="S13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1761,42 +1761,42 @@
         <v>408890.4</v>
       </c>
       <c r="M16" t="n">
-        <v>-586893.09</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>243.5</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>-411318.82</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>200.6</v>
+        <v>100</v>
       </c>
       <c r="Q16" t="n">
-        <v>-446433.68</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>209.2</v>
+        <v>100</v>
       </c>
       <c r="S16" t="n">
-        <v>-528662.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>229.3</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>-411318.82</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>200.6</v>
+        <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>exp_smoothing</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>200.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2605,42 +2605,42 @@
         <v>414450</v>
       </c>
       <c r="M26" t="n">
-        <v>-9400000</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2368.1</v>
+        <v>100</v>
       </c>
       <c r="O26" t="n">
-        <v>-4708070.05</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1236</v>
+        <v>100</v>
       </c>
       <c r="Q26" t="n">
-        <v>-6185988.53</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1592.6</v>
+        <v>100</v>
       </c>
       <c r="S26" t="n">
-        <v>-7616707.2</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1937.8</v>
+        <v>100</v>
       </c>
       <c r="U26" t="n">
-        <v>-7646175.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1944.9</v>
+        <v>100</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>1236</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -4573,34 +4573,34 @@
         <v>10000</v>
       </c>
       <c r="M49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>100</v>
       </c>
       <c r="O49" t="n">
-        <v>-24700.75</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>347</v>
+        <v>100</v>
       </c>
       <c r="Q49" t="n">
-        <v>-18083.17</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>280.8</v>
+        <v>100</v>
       </c>
       <c r="S49" t="n">
-        <v>-4848</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>148.5</v>
+        <v>100</v>
       </c>
       <c r="U49" t="n">
-        <v>-24700.75</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>347</v>
+        <v>100</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5805,34 +5805,34 @@
         <v>6729370.7</v>
       </c>
       <c r="M63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="O63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="S63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="U63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="X63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -8321,42 +8321,42 @@
         <v>356757.02</v>
       </c>
       <c r="M92" t="n">
-        <v>-1863158</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>622.2</v>
+        <v>100</v>
       </c>
       <c r="O92" t="n">
-        <v>-961554.6</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>369.5</v>
+        <v>100</v>
       </c>
       <c r="Q92" t="n">
-        <v>-1140792.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>419.8</v>
+        <v>100</v>
       </c>
       <c r="S92" t="n">
-        <v>-1499267.7</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>520.2</v>
+        <v>100</v>
       </c>
       <c r="U92" t="n">
-        <v>-961889.61</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>369.6</v>
+        <v>100</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="X92" t="n">
-        <v>369.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -9149,23 +9149,23 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>-1466683.5</v>
+        <v>0</v>
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="n">
-        <v>-1466683.5</v>
+        <v>0</v>
       </c>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="n">
-        <v>-150427.95</v>
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="n">
-        <v>-1466683.5</v>
+        <v>0</v>
       </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
@@ -9403,22 +9403,22 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>-166267</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>124.5</v>
+        <v>100</v>
       </c>
       <c r="Q105" t="n">
-        <v>-166267</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>124.5</v>
+        <v>100</v>
       </c>
       <c r="S105" t="n">
-        <v>-166267</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>124.5</v>
+        <v>100</v>
       </c>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="X105" t="n">
-        <v>124.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106">
@@ -10555,19 +10555,19 @@
         <v>139860</v>
       </c>
       <c r="M13" t="n">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1060270.49</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1314860</v>
+        <v>-139860</v>
       </c>
       <c r="Q13" t="n">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -10780,23 +10780,23 @@
         <v>408890.4</v>
       </c>
       <c r="M16" t="n">
-        <v>-411318.82</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>116172.33</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-820209.22</v>
+        <v>-408890.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>200.6</v>
+        <v>100</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>exp_smoothing</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -11500,23 +11500,23 @@
         <v>414450</v>
       </c>
       <c r="M26" t="n">
-        <v>-4708070.05</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4046011.83</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-5122520.05</v>
+        <v>-414450</v>
       </c>
       <c r="Q26" t="n">
-        <v>1236</v>
+        <v>100</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -13195,13 +13195,13 @@
         <v>10000</v>
       </c>
       <c r="M49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>56152.06</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>-10000</v>
@@ -14245,19 +14245,19 @@
         <v>6729370.7</v>
       </c>
       <c r="M63" t="n">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>2150890.4</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-7729370.7</v>
+        <v>-6729370.7</v>
       </c>
       <c r="Q63" t="n">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -16390,23 +16390,23 @@
         <v>356757.02</v>
       </c>
       <c r="M92" t="n">
-        <v>-961554.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>559327.72</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-1318311.62</v>
+        <v>-356757.02</v>
       </c>
       <c r="Q92" t="n">
-        <v>369.5</v>
+        <v>100</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>average</t>
+          <t>linear_trend</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -17331,15 +17331,15 @@
         <v>677423</v>
       </c>
       <c r="M105" t="n">
-        <v>-166267</v>
+        <v>0</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>-843690</v>
+        <v>-677423</v>
       </c>
       <c r="Q105" t="n">
-        <v>124.5</v>
+        <v>100</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
